--- a/mosip_master/xlsx/daysofweek_list.xlsx
+++ b/mosip_master/xlsx/daysofweek_list.xlsx
@@ -1,37 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\MASTER DATA\Master DAta Final\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karthik.s\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951DC107-49E9-455A-B252-0097F8258FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{039CB65F-62C1-4411-BE5B-003478BB9A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A8FEB07-6C5E-450E-A07D-C4611D4FA985}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4F810643-7225-4A2F-86F6-397780592148}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="daysofweek_list_202504151159" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -74,31 +58,31 @@
     <t>del_dtimes</t>
   </si>
   <si>
+    <t>MON</t>
+  </si>
+  <si>
+    <t>eng</t>
+  </si>
+  <si>
+    <t>globaladmin</t>
+  </si>
+  <si>
+    <t>TUE</t>
+  </si>
+  <si>
+    <t>WED</t>
+  </si>
+  <si>
+    <t>THU</t>
+  </si>
+  <si>
+    <t>FRI</t>
+  </si>
+  <si>
+    <t>SAT</t>
+  </si>
+  <si>
     <t>SUN</t>
-  </si>
-  <si>
-    <t>eng</t>
-  </si>
-  <si>
-    <t>MON</t>
-  </si>
-  <si>
-    <t>TUE</t>
-  </si>
-  <si>
-    <t>WED</t>
-  </si>
-  <si>
-    <t>THU</t>
-  </si>
-  <si>
-    <t>FRI</t>
-  </si>
-  <si>
-    <t>SAT</t>
-  </si>
-  <si>
-    <t>globaladmin</t>
   </si>
   <si>
     <t>now()</t>
@@ -108,7 +92,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,19 +103,313 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -140,109 +418,204 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color theme="4" tint="0.39997558519241921"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="47" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -573,285 +946,250 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7072505-77AC-4801-B41D-EA802F5C89EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7891A4BA-4A77-4C10-B88F-2FD9533F0217}">
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="4"/>
-    <col min="4" max="4" width="17.140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="14" style="4" customWidth="1"/>
-    <col min="6" max="7" width="9.140625" style="4"/>
-    <col min="8" max="8" width="11.140625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" style="4"/>
-    <col min="10" max="10" width="15.140625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="11" style="4" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="4"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>101</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="7">
-        <v>1</v>
-      </c>
-      <c r="D2" s="8" t="b">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="b">
         <v>0</v>
       </c>
-      <c r="E2" s="6" t="s">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" s="6" t="s">
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>103</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>104</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>105</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>106</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>107</v>
+      </c>
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="8" t="b">
+      <c r="K8" t="b">
         <v>0</v>
       </c>
-      <c r="L2" s="10"/>
-    </row>
-    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
-        <v>102</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="7">
-        <v>2</v>
-      </c>
-      <c r="D3" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" s="10"/>
-    </row>
-    <row r="4" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
-        <v>103</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7">
-        <v>3</v>
-      </c>
-      <c r="D4" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="10"/>
-    </row>
-    <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
-        <v>104</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="7">
-        <v>4</v>
-      </c>
-      <c r="D5" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="10"/>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
-        <v>105</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7">
-        <v>5</v>
-      </c>
-      <c r="D6" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" s="10"/>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
-        <v>106</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="7">
-        <v>6</v>
-      </c>
-      <c r="D7" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" s="10"/>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
-        <v>107</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="7">
-        <v>7</v>
-      </c>
-      <c r="D8" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
